--- a/testdata/lead/bulk_upload/amit_contact.xlsx
+++ b/testdata/lead/bulk_upload/amit_contact.xlsx
@@ -412,57 +412,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Rajendra Kaniyar</v>
+        <v>Bhramar Agarwal</v>
       </c>
       <c r="B2" t="str">
-        <v>rajendra.kaniyar401@gmail.com</v>
+        <v>bhramar.agarwal127@gmail.com</v>
       </c>
       <c r="C2">
-        <v>7060849549</v>
+        <v>7916356629</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Vaishnavi Johar</v>
+        <v>Gajbaahu Pilla</v>
       </c>
       <c r="B3" t="str">
-        <v>vaishnavi.johar654@gmail.com</v>
+        <v>gajbaahu.pilla480@gmail.com</v>
       </c>
       <c r="C3">
-        <v>8832725392</v>
+        <v>8795278638</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Trilochana Kaniyar</v>
+        <v>Dayaamay Namboothiri</v>
       </c>
       <c r="B4" t="str">
-        <v>trilochana.kaniyar148@gmail.com</v>
+        <v>dayaamay.namboothiri917@gmail.com</v>
       </c>
       <c r="C4">
-        <v>7023053312</v>
+        <v>7016214842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Meenakshi Dubashi</v>
+        <v>Navin Ahluwalia-Dwivedi</v>
       </c>
       <c r="B5" t="str">
-        <v>meenakshi.dubashi236@gmail.com</v>
+        <v>navin.ahluwaliadwivedi534@gmail.com</v>
       </c>
       <c r="C5">
-        <v>7956471120</v>
+        <v>9673963770</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Akshata Nayar</v>
+        <v>Chidambaram Joshi</v>
       </c>
       <c r="B6" t="str">
-        <v>akshata.nayar305@gmail.com</v>
+        <v>chidambaram.joshi841@gmail.com</v>
       </c>
       <c r="C6">
-        <v>8717587320</v>
+        <v>9932840423</v>
       </c>
     </row>
   </sheetData>
